--- a/forecast_2026.xlsx
+++ b/forecast_2026.xlsx
@@ -467,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6638.75</v>
+        <v>7837.82</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>13442.5</v>
+        <v>12622.6</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>13137.21</v>
+        <v>16212.43</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>23793.91</v>
+        <v>26011.36</v>
       </c>
     </row>
     <row r="6">
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>11489.28</v>
+        <v>9463.219999999999</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5600.93</v>
+        <v>3338.54</v>
       </c>
     </row>
     <row r="8">
@@ -563,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2026.13</v>
+        <v>-397.03</v>
       </c>
     </row>
     <row r="9">
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7035.3</v>
+        <v>5803.96</v>
       </c>
     </row>
     <row r="10">
@@ -595,7 +595,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>10801.23</v>
+        <v>13518.5</v>
       </c>
     </row>
     <row r="11">
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12816.8</v>
+        <v>16341.61</v>
       </c>
     </row>
     <row r="12">
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>27339.41</v>
+        <v>23011.25</v>
       </c>
     </row>
     <row r="13">
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12327.94</v>
+        <v>12586.7</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2275.77</v>
+        <v>6462.02</v>
       </c>
     </row>
     <row r="15">
@@ -675,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2119.38</v>
+        <v>-267.85</v>
       </c>
     </row>
     <row r="16">
@@ -691,7 +691,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6150.2</v>
+        <v>2938.84</v>
       </c>
     </row>
     <row r="17">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>12944.71</v>
+        <v>9886.67</v>
       </c>
     </row>
     <row r="18">
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>15216.48</v>
+        <v>15839.06</v>
       </c>
     </row>
     <row r="19">
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>27251.31</v>
+        <v>26269.71</v>
       </c>
     </row>
     <row r="20">
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>11641.92</v>
+        <v>12850.86</v>
       </c>
     </row>
     <row r="21">
@@ -771,7 +771,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5669.24</v>
+        <v>6726.18</v>
       </c>
     </row>
     <row r="22">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1160.93</v>
+        <v>3622.33</v>
       </c>
     </row>
     <row r="23">
@@ -803,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6425.38</v>
+        <v>3068.01</v>
       </c>
     </row>
     <row r="24">
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13046.56</v>
+        <v>13145.13</v>
       </c>
     </row>
     <row r="25">
@@ -835,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15203.84</v>
+        <v>15968.24</v>
       </c>
     </row>
     <row r="26">
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>27332.89</v>
+        <v>26398.89</v>
       </c>
     </row>
     <row r="27">
@@ -867,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8434.030000000001</v>
+        <v>12845.06</v>
       </c>
     </row>
     <row r="28">
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>5711.73</v>
+        <v>3726.07</v>
       </c>
     </row>
     <row r="29">
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>2212.5</v>
+        <v>3119.79</v>
       </c>
     </row>
     <row r="30">
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3051.75</v>
+        <v>6326.47</v>
       </c>
     </row>
     <row r="31">
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>13207.14</v>
+        <v>10145.03</v>
       </c>
     </row>
     <row r="32">
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>13138.64</v>
+        <v>16729.14</v>
       </c>
     </row>
     <row r="33">
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>27389.26</v>
+        <v>23398.78</v>
       </c>
     </row>
     <row r="34">
@@ -979,7 +979,7 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>11888.36</v>
+        <v>9979.93</v>
       </c>
     </row>
     <row r="35">
@@ -995,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>6516.08</v>
+        <v>6849.55</v>
       </c>
     </row>
     <row r="36">
@@ -1011,7 +1011,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>2994.46</v>
+        <v>3113.99</v>
       </c>
     </row>
     <row r="37">
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3135.43</v>
+        <v>6320.67</v>
       </c>
     </row>
     <row r="38">
@@ -1043,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>13165.55</v>
+        <v>13403.49</v>
       </c>
     </row>
     <row r="39">
@@ -1059,7 +1059,7 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>15464.4</v>
+        <v>13097.31</v>
       </c>
     </row>
     <row r="40">
@@ -1075,7 +1075,7 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>24176.06</v>
+        <v>27288.97</v>
       </c>
     </row>
     <row r="41">
@@ -1091,7 +1091,7 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>11841.01</v>
+        <v>13238.39</v>
       </c>
     </row>
     <row r="42">
@@ -1107,7 +1107,7 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>5958.66</v>
+        <v>3984.42</v>
       </c>
     </row>
     <row r="43">
@@ -1123,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>2333.78</v>
+        <v>3378.14</v>
       </c>
     </row>
     <row r="44">
@@ -1139,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>6584.96</v>
+        <v>3455.55</v>
       </c>
     </row>
     <row r="45">
@@ -1155,7 +1155,7 @@
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>13956.85</v>
+        <v>13397.69</v>
       </c>
     </row>
     <row r="46">
@@ -1171,7 +1171,7 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>15422.14</v>
+        <v>16355.77</v>
       </c>
     </row>
     <row r="47">
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>24238.66</v>
+        <v>27418.14</v>
       </c>
     </row>
     <row r="48">
@@ -1203,7 +1203,7 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>11904.38</v>
+        <v>13367.56</v>
       </c>
     </row>
     <row r="49">
@@ -1219,7 +1219,7 @@
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>5911.49</v>
+        <v>7242.88</v>
       </c>
     </row>
     <row r="50">
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>2395.4</v>
+        <v>3507.32</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>6539.75</v>
+        <v>3584.72</v>
       </c>
     </row>
     <row r="52">
@@ -1267,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>14022.51</v>
+        <v>13526.86</v>
       </c>
     </row>
     <row r="53">
@@ -1283,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>13319.56</v>
+        <v>16349.97</v>
       </c>
     </row>
     <row r="54">
@@ -1299,7 +1299,7 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>28314.86</v>
+        <v>26780.62</v>
       </c>
     </row>
     <row r="55">
@@ -1315,7 +1315,7 @@
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>12699.39</v>
+        <v>13361.76</v>
       </c>
     </row>
     <row r="56">
@@ -1331,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>2693.94</v>
+        <v>7372.06</v>
       </c>
     </row>
     <row r="57">
@@ -1347,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3191.2</v>
+        <v>3501.52</v>
       </c>
     </row>
     <row r="58">
@@ -1363,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>6715.43</v>
+        <v>3713.9</v>
       </c>
     </row>
     <row r="59">
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>13355.49</v>
+        <v>10661.74</v>
       </c>
     </row>
     <row r="60">
@@ -1395,7 +1395,7 @@
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>15662.02</v>
+        <v>13484.84</v>
       </c>
     </row>
     <row r="61">
@@ -1411,7 +1411,7 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>27761.46</v>
+        <v>27044.77</v>
       </c>
     </row>
     <row r="62">
@@ -1427,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>12146.15</v>
+        <v>13625.92</v>
       </c>
     </row>
     <row r="63">
@@ -1443,7 +1443,7 @@
         <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>6152.59</v>
+        <v>7501.24</v>
       </c>
     </row>
     <row r="64">
@@ -1459,7 +1459,7 @@
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>-756.5</v>
+        <v>3630.69</v>
       </c>
     </row>
     <row r="65">
@@ -1475,7 +1475,7 @@
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>6780.36</v>
+        <v>6972.36</v>
       </c>
     </row>
     <row r="66">
@@ -1491,7 +1491,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>13533.21</v>
+        <v>13920.2</v>
       </c>
     </row>
     <row r="67">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>15612.3</v>
+        <v>16743.3</v>
       </c>
     </row>
     <row r="68">
@@ -1523,7 +1523,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>27825.75</v>
+        <v>24044.67</v>
       </c>
     </row>
     <row r="69">
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>8816.27</v>
+        <v>13620.12</v>
       </c>
     </row>
     <row r="70">
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>6216.57</v>
+        <v>4501.13</v>
       </c>
     </row>
     <row r="71">
@@ -1571,7 +1571,7 @@
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>3319.23</v>
+        <v>3759.87</v>
       </c>
     </row>
     <row r="72">
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>3450.07</v>
+        <v>6966.56</v>
       </c>
     </row>
     <row r="73">
@@ -1603,7 +1603,7 @@
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>13597.23</v>
+        <v>10920.09</v>
       </c>
     </row>
     <row r="74">
@@ -1619,7 +1619,7 @@
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>15790</v>
+        <v>13743.19</v>
       </c>
     </row>
     <row r="75">
@@ -1635,7 +1635,7 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>24495.74</v>
+        <v>27168.15</v>
       </c>
     </row>
     <row r="76">
@@ -1651,7 +1651,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>12161.23</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="77">
@@ -1667,7 +1667,7 @@
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>6167.53</v>
+        <v>8391.32</v>
       </c>
     </row>
     <row r="78">
@@ -1683,7 +1683,7 @@
         <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>-628.0599999999999</v>
+        <v>3889.05</v>
       </c>
     </row>
     <row r="79">
@@ -1699,7 +1699,7 @@
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>6908.48</v>
+        <v>4101.43</v>
       </c>
     </row>
     <row r="80">
@@ -1715,7 +1715,7 @@
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>13661.44</v>
+        <v>14178.55</v>
       </c>
     </row>
     <row r="81">
@@ -1731,7 +1731,7 @@
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>15854.03</v>
+        <v>13872.37</v>
       </c>
     </row>
     <row r="82">
@@ -1747,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>24559.92</v>
+        <v>27297.33</v>
       </c>
     </row>
     <row r="83">
@@ -1763,7 +1763,7 @@
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>12225.4</v>
+        <v>14645.17</v>
       </c>
     </row>
     <row r="84">
@@ -1779,7 +1779,7 @@
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>6344.92</v>
+        <v>7888.77</v>
       </c>
     </row>
     <row r="85">
@@ -1795,7 +1795,7 @@
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>2830.24</v>
+        <v>1023.92</v>
       </c>
     </row>
     <row r="86">
@@ -1811,7 +1811,7 @@
         <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>6972.56</v>
+        <v>7359.89</v>
       </c>
     </row>
     <row r="87">
@@ -1827,7 +1827,7 @@
         <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>13725.57</v>
+        <v>14307.73</v>
       </c>
     </row>
     <row r="88">
@@ -1843,7 +1843,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>15804.97</v>
+        <v>17762.55</v>
       </c>
     </row>
     <row r="89">
@@ -1859,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>27904.9</v>
+        <v>28193.21</v>
       </c>
     </row>
     <row r="90">
@@ -1875,7 +1875,7 @@
         <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>9008.709999999999</v>
+        <v>14007.65</v>
       </c>
     </row>
     <row r="91">
@@ -1891,7 +1891,7 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>6409.09</v>
+        <v>8017.95</v>
       </c>
     </row>
     <row r="92">
@@ -1907,7 +1907,7 @@
         <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>2894.37</v>
+        <v>1153.1</v>
       </c>
     </row>
     <row r="93">
@@ -1923,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>6923.48</v>
+        <v>8120.79</v>
       </c>
     </row>
     <row r="94">
@@ -1939,7 +1939,7 @@
         <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>11512.8</v>
+        <v>14301.93</v>
       </c>
     </row>
     <row r="95">
@@ -1955,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>15869.1</v>
+        <v>17260.01</v>
       </c>
     </row>
     <row r="96">
@@ -1971,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>24688.23</v>
+        <v>27555.68</v>
       </c>
     </row>
     <row r="97">
@@ -1987,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>12466.97</v>
+        <v>14271.81</v>
       </c>
     </row>
     <row r="98">
@@ -2003,7 +2003,7 @@
         <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>6359.97</v>
+        <v>8147.13</v>
       </c>
     </row>
     <row r="99">
@@ -2019,7 +2019,7 @@
         <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>2958.54</v>
+        <v>4411.56</v>
       </c>
     </row>
     <row r="100">
@@ -2035,7 +2035,7 @@
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>7100.89</v>
+        <v>4488.96</v>
       </c>
     </row>
     <row r="101">
@@ -2051,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>13853.89</v>
+        <v>11436.8</v>
       </c>
     </row>
     <row r="102">
@@ -2067,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>16046.54</v>
+        <v>14259.9</v>
       </c>
     </row>
     <row r="103">
@@ -2083,7 +2083,7 @@
         <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>28033.22</v>
+        <v>28451.56</v>
       </c>
     </row>
     <row r="104">
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>12531.13</v>
+        <v>14400.98</v>
       </c>
     </row>
     <row r="105">
@@ -2115,7 +2115,7 @@
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>6424.13</v>
+        <v>8276.299999999999</v>
       </c>
     </row>
     <row r="106">
@@ -2131,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>3639.93</v>
+        <v>4405.76</v>
       </c>
     </row>
     <row r="107">
@@ -2147,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>7165.05</v>
+        <v>4618.14</v>
       </c>
     </row>
     <row r="108">
@@ -2163,7 +2163,7 @@
         <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>13918.05</v>
+        <v>14695.26</v>
       </c>
     </row>
     <row r="109">
@@ -2179,7 +2179,7 @@
         <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>13833.75</v>
+        <v>17383.39</v>
       </c>
     </row>
     <row r="110">
@@ -2195,7 +2195,7 @@
         <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>28210.64</v>
+        <v>24819.73</v>
       </c>
     </row>
     <row r="111">
@@ -2211,7 +2211,7 @@
         <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>12595.28</v>
+        <v>11400.88</v>
       </c>
     </row>
     <row r="112">
@@ -2227,7 +2227,7 @@
         <v>4</v>
       </c>
       <c r="D112" t="n">
-        <v>6601.55</v>
+        <v>8405.48</v>
       </c>
     </row>
     <row r="113">
@@ -2243,7 +2243,7 @@
         <v>4</v>
       </c>
       <c r="D113" t="n">
-        <v>3086.85</v>
+        <v>1540.63</v>
       </c>
     </row>
     <row r="114">
@@ -2259,7 +2259,7 @@
         <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>7846.45</v>
+        <v>7741.62</v>
       </c>
     </row>
     <row r="115">
@@ -2275,7 +2275,7 @@
         <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>11705.26</v>
+        <v>14689.46</v>
       </c>
     </row>
     <row r="116">
@@ -2291,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>16061.58</v>
+        <v>18279.26</v>
       </c>
     </row>
     <row r="117">
@@ -2307,7 +2307,7 @@
         <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>24880.69</v>
+        <v>27943.21</v>
       </c>
     </row>
     <row r="118">
@@ -2323,7 +2323,7 @@
         <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>9265.33</v>
+        <v>14524.36</v>
       </c>
     </row>
     <row r="119">
@@ -2339,7 +2339,7 @@
         <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>6665.71</v>
+        <v>5405.37</v>
       </c>
     </row>
     <row r="120">
@@ -2355,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>-243.1</v>
+        <v>4664.11</v>
       </c>
     </row>
     <row r="121">
@@ -2371,7 +2371,7 @@
         <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>7180.1</v>
+        <v>8005.78</v>
       </c>
     </row>
     <row r="122">
@@ -2387,7 +2387,7 @@
         <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>11769.42</v>
+        <v>14818.64</v>
       </c>
     </row>
     <row r="123">
@@ -2403,7 +2403,7 @@
         <v>5</v>
       </c>
       <c r="D123" t="n">
-        <v>13962.06</v>
+        <v>17641.74</v>
       </c>
     </row>
     <row r="124">
@@ -2419,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="D124" t="n">
-        <v>28338.95</v>
+        <v>28207.37</v>
       </c>
     </row>
     <row r="125">
@@ -2435,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="D125" t="n">
-        <v>12723.59</v>
+        <v>11659.23</v>
       </c>
     </row>
     <row r="126">
@@ -2451,7 +2451,7 @@
         <v>5</v>
       </c>
       <c r="D126" t="n">
-        <v>6729.86</v>
+        <v>5534.55</v>
       </c>
     </row>
     <row r="127">
@@ -2467,7 +2467,7 @@
         <v>5</v>
       </c>
       <c r="D127" t="n">
-        <v>3215.16</v>
+        <v>4928.27</v>
       </c>
     </row>
     <row r="128">
@@ -2483,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="D128" t="n">
-        <v>3963.41</v>
+        <v>7999.98</v>
       </c>
     </row>
     <row r="129">
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="D129" t="n">
-        <v>11833.57</v>
+        <v>14947.81</v>
       </c>
     </row>
     <row r="130">
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>16303.15</v>
+        <v>14776.61</v>
       </c>
     </row>
     <row r="131">
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>28289.84</v>
+        <v>28336.55</v>
       </c>
     </row>
     <row r="132">
@@ -2547,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="D132" t="n">
-        <v>12787.75</v>
+        <v>14917.69</v>
       </c>
     </row>
     <row r="133">
@@ -2563,7 +2563,7 @@
         <v>5</v>
       </c>
       <c r="D133" t="n">
-        <v>6794.02</v>
+        <v>5663.73</v>
       </c>
     </row>
     <row r="134">
@@ -2579,7 +2579,7 @@
         <v>5</v>
       </c>
       <c r="D134" t="n">
-        <v>3279.31</v>
+        <v>1928.16</v>
       </c>
     </row>
     <row r="135">
@@ -2595,7 +2595,7 @@
         <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>7421.67</v>
+        <v>8264.129999999999</v>
       </c>
     </row>
     <row r="136">
@@ -2611,7 +2611,7 @@
         <v>5</v>
       </c>
       <c r="D136" t="n">
-        <v>14791.91</v>
+        <v>15076.99</v>
       </c>
     </row>
     <row r="137">
@@ -2627,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>16367.31</v>
+        <v>18035.07</v>
       </c>
     </row>
     <row r="138">
@@ -2643,7 +2643,7 @@
         <v>5</v>
       </c>
       <c r="D138" t="n">
-        <v>28353.99</v>
+        <v>28465.72</v>
       </c>
     </row>
     <row r="139">
@@ -2659,7 +2659,7 @@
         <v>5</v>
       </c>
       <c r="D139" t="n">
-        <v>12738.64</v>
+        <v>15678.59</v>
       </c>
     </row>
     <row r="140">
@@ -2675,7 +2675,7 @@
         <v>5</v>
       </c>
       <c r="D140" t="n">
-        <v>6858.17</v>
+        <v>8922.190000000001</v>
       </c>
     </row>
     <row r="141">
@@ -2691,7 +2691,7 @@
         <v>5</v>
       </c>
       <c r="D141" t="n">
-        <v>3960.71</v>
+        <v>5051.64</v>
       </c>
     </row>
     <row r="142">
@@ -2707,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="D142" t="n">
-        <v>8103.07</v>
+        <v>8258.33</v>
       </c>
     </row>
     <row r="143">
@@ -2723,7 +2723,7 @@
         <v>5</v>
       </c>
       <c r="D143" t="n">
-        <v>14238.82</v>
+        <v>15341.15</v>
       </c>
     </row>
     <row r="144">
@@ -2739,7 +2739,7 @@
         <v>5</v>
       </c>
       <c r="D144" t="n">
-        <v>16431.46</v>
+        <v>18164.25</v>
       </c>
     </row>
     <row r="145">
@@ -2755,7 +2755,7 @@
         <v>5</v>
       </c>
       <c r="D145" t="n">
-        <v>28531.42</v>
+        <v>28594.9</v>
       </c>
     </row>
     <row r="146">
@@ -2771,7 +2771,7 @@
         <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>12916.06</v>
+        <v>15176.05</v>
       </c>
     </row>
     <row r="147">
@@ -2787,7 +2787,7 @@
         <v>5</v>
       </c>
       <c r="D147" t="n">
-        <v>6922.33</v>
+        <v>5922.08</v>
       </c>
     </row>
     <row r="148">
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="D148" t="n">
-        <v>3294.35</v>
+        <v>5947.52</v>
       </c>
     </row>
     <row r="149">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="D149" t="n">
-        <v>7436.72</v>
+        <v>8522.49</v>
       </c>
     </row>
     <row r="150">
@@ -2835,7 +2835,7 @@
         <v>5</v>
       </c>
       <c r="D150" t="n">
-        <v>14302.98</v>
+        <v>12341.04</v>
       </c>
     </row>
     <row r="151">
@@ -2851,7 +2851,7 @@
         <v>5</v>
       </c>
       <c r="D151" t="n">
-        <v>16495.62</v>
+        <v>18293.43</v>
       </c>
     </row>
     <row r="152">
@@ -2867,7 +2867,7 @@
         <v>5</v>
       </c>
       <c r="D152" t="n">
-        <v>29212.81</v>
+        <v>28589.1</v>
       </c>
     </row>
     <row r="153">
@@ -2883,7 +2883,7 @@
         <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>12980.21</v>
+        <v>12175.94</v>
       </c>
     </row>
     <row r="154">
@@ -2899,7 +2899,7 @@
         <v>6</v>
       </c>
       <c r="D154" t="n">
-        <v>6986.48</v>
+        <v>6051.26</v>
       </c>
     </row>
     <row r="155">
@@ -2915,7 +2915,7 @@
         <v>6</v>
       </c>
       <c r="D155" t="n">
-        <v>3358.51</v>
+        <v>5444.98</v>
       </c>
     </row>
     <row r="156">
@@ -2931,7 +2931,7 @@
         <v>6</v>
       </c>
       <c r="D156" t="n">
-        <v>8231.379999999999</v>
+        <v>8516.690000000001</v>
       </c>
     </row>
     <row r="157">
@@ -2947,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="D157" t="n">
-        <v>14367.13</v>
+        <v>12470.22</v>
       </c>
     </row>
     <row r="158">
@@ -2963,7 +2963,7 @@
         <v>6</v>
       </c>
       <c r="D158" t="n">
-        <v>16446.51</v>
+        <v>19054.33</v>
       </c>
     </row>
     <row r="159">
@@ -2979,7 +2979,7 @@
         <v>6</v>
       </c>
       <c r="D159" t="n">
-        <v>25265.62</v>
+        <v>28718.28</v>
       </c>
     </row>
     <row r="160">
@@ -2995,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="D160" t="n">
-        <v>13044.37</v>
+        <v>12305.12</v>
       </c>
     </row>
     <row r="161">
@@ -3011,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>3656.53</v>
+        <v>9941.440000000001</v>
       </c>
     </row>
     <row r="162">
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="D162" t="n">
-        <v>3535.93</v>
+        <v>5574.15</v>
       </c>
     </row>
     <row r="163">
@@ -3043,7 +3043,7 @@
         <v>6</v>
       </c>
       <c r="D163" t="n">
-        <v>7565.03</v>
+        <v>9412.559999999999</v>
       </c>
     </row>
     <row r="164">
@@ -3059,7 +3059,7 @@
         <v>6</v>
       </c>
       <c r="D164" t="n">
-        <v>14318.02</v>
+        <v>16360.4</v>
       </c>
     </row>
     <row r="165">
@@ -3075,7 +3075,7 @@
         <v>6</v>
       </c>
       <c r="D165" t="n">
-        <v>16510.66</v>
+        <v>18551.78</v>
       </c>
     </row>
     <row r="166">
@@ -3091,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="D166" t="n">
-        <v>28723.88</v>
+        <v>25853.15</v>
       </c>
     </row>
     <row r="167">
@@ -3107,7 +3107,7 @@
         <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>9714.42</v>
+        <v>15428.6</v>
       </c>
     </row>
     <row r="168">
@@ -3123,7 +3123,7 @@
         <v>6</v>
       </c>
       <c r="D168" t="n">
-        <v>7114.79</v>
+        <v>9438.9</v>
       </c>
     </row>
     <row r="169">
@@ -3139,7 +3139,7 @@
         <v>6</v>
       </c>
       <c r="D169" t="n">
-        <v>3600.09</v>
+        <v>2574.05</v>
       </c>
     </row>
     <row r="170">
@@ -3155,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="D170" t="n">
-        <v>7742.45</v>
+        <v>5780.74</v>
       </c>
     </row>
     <row r="171">
@@ -3171,7 +3171,7 @@
         <v>6</v>
       </c>
       <c r="D171" t="n">
-        <v>14382.18</v>
+        <v>15857.85</v>
       </c>
     </row>
     <row r="172">
@@ -3187,7 +3187,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="n">
-        <v>16574.82</v>
+        <v>19312.68</v>
       </c>
     </row>
     <row r="173">
@@ -3203,7 +3203,7 @@
         <v>6</v>
       </c>
       <c r="D173" t="n">
-        <v>28788.04</v>
+        <v>25982.33</v>
       </c>
     </row>
     <row r="174">
@@ -3219,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="D174" t="n">
-        <v>13059.41</v>
+        <v>15692.75</v>
       </c>
     </row>
     <row r="175">
@@ -3235,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="D175" t="n">
-        <v>7178.95</v>
+        <v>6438.79</v>
       </c>
     </row>
     <row r="176">
@@ -3251,7 +3251,7 @@
         <v>6</v>
       </c>
       <c r="D176" t="n">
-        <v>3550.98</v>
+        <v>6464.23</v>
       </c>
     </row>
     <row r="177">
@@ -3267,7 +3267,7 @@
         <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>7806.6</v>
+        <v>5909.91</v>
       </c>
     </row>
     <row r="178">
@@ -3283,7 +3283,7 @@
         <v>6</v>
       </c>
       <c r="D178" t="n">
-        <v>14446.33</v>
+        <v>16618.75</v>
       </c>
     </row>
     <row r="179">
@@ -3299,7 +3299,7 @@
         <v>6</v>
       </c>
       <c r="D179" t="n">
-        <v>16752.24</v>
+        <v>18810.14</v>
       </c>
     </row>
     <row r="180">
@@ -3315,7 +3315,7 @@
         <v>6</v>
       </c>
       <c r="D180" t="n">
-        <v>29469.43</v>
+        <v>29105.81</v>
       </c>
     </row>
     <row r="181">
@@ -3331,7 +3331,7 @@
         <v>6</v>
       </c>
       <c r="D181" t="n">
-        <v>13236.83</v>
+        <v>12692.65</v>
       </c>
     </row>
     <row r="182">
@@ -3347,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="D182" t="n">
-        <v>7243.1</v>
+        <v>9697.25</v>
       </c>
     </row>
     <row r="183">
@@ -3363,7 +3363,7 @@
         <v>7</v>
       </c>
       <c r="D183" t="n">
-        <v>3728.4</v>
+        <v>2832.4</v>
       </c>
     </row>
     <row r="184">
@@ -3379,7 +3379,7 @@
         <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>8488</v>
+        <v>9033.4</v>
       </c>
     </row>
     <row r="185">
@@ -3395,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="D185" t="n">
-        <v>12346.82</v>
+        <v>15981.23</v>
       </c>
     </row>
     <row r="186">
@@ -3411,7 +3411,7 @@
         <v>7</v>
       </c>
       <c r="D186" t="n">
-        <v>16816.39</v>
+        <v>18939.31</v>
       </c>
     </row>
     <row r="187">
@@ -3427,7 +3427,7 @@
         <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>28803.08</v>
+        <v>30001.69</v>
       </c>
     </row>
     <row r="188">
@@ -3443,7 +3443,7 @@
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>9906.889999999999</v>
+        <v>15816.13</v>
       </c>
     </row>
     <row r="189">
@@ -3459,7 +3459,7 @@
         <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>7193.99</v>
+        <v>9826.43</v>
       </c>
     </row>
     <row r="190">
@@ -3475,7 +3475,7 @@
         <v>7</v>
       </c>
       <c r="D190" t="n">
-        <v>3679.29</v>
+        <v>6090.86</v>
       </c>
     </row>
     <row r="191">
@@ -3491,7 +3491,7 @@
         <v>7</v>
       </c>
       <c r="D191" t="n">
-        <v>7934.91</v>
+        <v>6168.27</v>
       </c>
     </row>
     <row r="192">
@@ -3507,7 +3507,7 @@
         <v>7</v>
       </c>
       <c r="D192" t="n">
-        <v>14687.91</v>
+        <v>13116.1</v>
       </c>
     </row>
     <row r="193">
@@ -3523,7 +3523,7 @@
         <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>14603.61</v>
+        <v>18933.51</v>
       </c>
     </row>
     <row r="194">
@@ -3539,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="D194" t="n">
-        <v>29597.74</v>
+        <v>29364.16</v>
       </c>
     </row>
     <row r="195">
@@ -3555,7 +3555,7 @@
         <v>7</v>
       </c>
       <c r="D195" t="n">
-        <v>13251.88</v>
+        <v>16712.01</v>
       </c>
     </row>
     <row r="196">
@@ -3571,7 +3571,7 @@
         <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>7371.41</v>
+        <v>9955.610000000001</v>
       </c>
     </row>
     <row r="197">
@@ -3587,7 +3587,7 @@
         <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>3856.71</v>
+        <v>6220.04</v>
       </c>
     </row>
     <row r="198">
@@ -3603,7 +3603,7 @@
         <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>4604.97</v>
+        <v>10058.45</v>
       </c>
     </row>
     <row r="199">
@@ -3619,7 +3619,7 @@
         <v>7</v>
       </c>
       <c r="D199" t="n">
-        <v>12475.13</v>
+        <v>16239.59</v>
       </c>
     </row>
     <row r="200">
@@ -3635,7 +3635,7 @@
         <v>7</v>
       </c>
       <c r="D200" t="n">
-        <v>14667.77</v>
+        <v>19062.69</v>
       </c>
     </row>
     <row r="201">
@@ -3651,7 +3651,7 @@
         <v>7</v>
       </c>
       <c r="D201" t="n">
-        <v>25650.55</v>
+        <v>29493.34</v>
       </c>
     </row>
     <row r="202">
@@ -3667,7 +3667,7 @@
         <v>7</v>
       </c>
       <c r="D202" t="n">
-        <v>13316.03</v>
+        <v>16841.19</v>
       </c>
     </row>
     <row r="203">
@@ -3683,7 +3683,7 @@
         <v>7</v>
       </c>
       <c r="D203" t="n">
-        <v>7435.57</v>
+        <v>6955.5</v>
       </c>
     </row>
     <row r="204">
@@ -3699,7 +3699,7 @@
         <v>7</v>
       </c>
       <c r="D204" t="n">
-        <v>3920.86</v>
+        <v>3219.93</v>
       </c>
     </row>
     <row r="205">
@@ -3715,7 +3715,7 @@
         <v>7</v>
       </c>
       <c r="D205" t="n">
-        <v>4669.12</v>
+        <v>9420.93</v>
       </c>
     </row>
     <row r="206">
@@ -3731,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="D206" t="n">
-        <v>14702.95</v>
+        <v>17135.46</v>
       </c>
     </row>
     <row r="207">
@@ -3747,7 +3747,7 @@
         <v>7</v>
       </c>
       <c r="D207" t="n">
-        <v>17008.86</v>
+        <v>16197.56</v>
       </c>
     </row>
     <row r="208">
@@ -3763,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="D208" t="n">
-        <v>29108.81</v>
+        <v>26628.21</v>
       </c>
     </row>
     <row r="209">
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
       <c r="D209" t="n">
-        <v>13380.19</v>
+        <v>16970.36</v>
       </c>
     </row>
     <row r="210">
@@ -3795,7 +3795,7 @@
         <v>7</v>
       </c>
       <c r="D210" t="n">
-        <v>7499.72</v>
+        <v>7084.68</v>
       </c>
     </row>
     <row r="211">
@@ -3811,7 +3811,7 @@
         <v>7</v>
       </c>
       <c r="D211" t="n">
-        <v>3985.02</v>
+        <v>3349.11</v>
       </c>
     </row>
     <row r="212">
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>8014.11</v>
+        <v>9685.08</v>
       </c>
     </row>
     <row r="213">
@@ -3843,7 +3843,7 @@
         <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>14767.11</v>
+        <v>17264.64</v>
       </c>
     </row>
     <row r="214">
@@ -3859,7 +3859,7 @@
         <v>8</v>
       </c>
       <c r="D214" t="n">
-        <v>16959.75</v>
+        <v>20087.74</v>
       </c>
     </row>
     <row r="215">
@@ -3875,7 +3875,7 @@
         <v>8</v>
       </c>
       <c r="D215" t="n">
-        <v>29172.97</v>
+        <v>26757.39</v>
       </c>
     </row>
     <row r="216">
@@ -3891,7 +3891,7 @@
         <v>8</v>
       </c>
       <c r="D216" t="n">
-        <v>10163.51</v>
+        <v>17099.54</v>
       </c>
     </row>
     <row r="217">
@@ -3907,7 +3907,7 @@
         <v>8</v>
       </c>
       <c r="D217" t="n">
-        <v>7563.88</v>
+        <v>7213.85</v>
       </c>
     </row>
     <row r="218">
@@ -3923,7 +3923,7 @@
         <v>8</v>
       </c>
       <c r="D218" t="n">
-        <v>4049.17</v>
+        <v>6607.57</v>
       </c>
     </row>
     <row r="219">
@@ -3939,7 +3939,7 @@
         <v>8</v>
       </c>
       <c r="D219" t="n">
-        <v>4797.43</v>
+        <v>10445.98</v>
       </c>
     </row>
     <row r="220">
@@ -3955,7 +3955,7 @@
         <v>8</v>
       </c>
       <c r="D220" t="n">
-        <v>14831.26</v>
+        <v>17393.82</v>
       </c>
     </row>
     <row r="221">
@@ -3971,7 +3971,7 @@
         <v>8</v>
       </c>
       <c r="D221" t="n">
-        <v>14860.23</v>
+        <v>19450.22</v>
       </c>
     </row>
     <row r="222">
@@ -3987,7 +3987,7 @@
         <v>8</v>
       </c>
       <c r="D222" t="n">
-        <v>29123.86</v>
+        <v>30647.57</v>
       </c>
     </row>
     <row r="223">
@@ -4003,7 +4003,7 @@
         <v>8</v>
       </c>
       <c r="D223" t="n">
-        <v>13508.5</v>
+        <v>16596.99</v>
       </c>
     </row>
     <row r="224">
@@ -4019,7 +4019,7 @@
         <v>8</v>
       </c>
       <c r="D224" t="n">
-        <v>7628.03</v>
+        <v>7343.03</v>
       </c>
     </row>
     <row r="225">
@@ -4035,7 +4035,7 @@
         <v>8</v>
       </c>
       <c r="D225" t="n">
-        <v>4113.33</v>
+        <v>6736.75</v>
       </c>
     </row>
     <row r="226">
@@ -4051,7 +4051,7 @@
         <v>8</v>
       </c>
       <c r="D226" t="n">
-        <v>8255.690000000001</v>
+        <v>9943.440000000001</v>
       </c>
     </row>
     <row r="227">
@@ -4067,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="D227" t="n">
-        <v>15008.68</v>
+        <v>13761.99</v>
       </c>
     </row>
     <row r="228">
@@ -4083,7 +4083,7 @@
         <v>8</v>
       </c>
       <c r="D228" t="n">
-        <v>17818.57</v>
+        <v>19579.4</v>
       </c>
     </row>
     <row r="229">
@@ -4099,7 +4099,7 @@
         <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>29301.28</v>
+        <v>30145.03</v>
       </c>
     </row>
     <row r="230">
@@ -4115,7 +4115,7 @@
         <v>8</v>
       </c>
       <c r="D230" t="n">
-        <v>10291.82</v>
+        <v>16591.19</v>
       </c>
     </row>
     <row r="231">
@@ -4131,7 +4131,7 @@
         <v>8</v>
       </c>
       <c r="D231" t="n">
-        <v>7578.92</v>
+        <v>11233.22</v>
       </c>
     </row>
     <row r="232">
@@ -4147,7 +4147,7 @@
         <v>8</v>
       </c>
       <c r="D232" t="n">
-        <v>783.38</v>
+        <v>6730.95</v>
       </c>
     </row>
     <row r="233">
@@ -4163,7 +4163,7 @@
         <v>8</v>
       </c>
       <c r="D233" t="n">
-        <v>8206.58</v>
+        <v>10072.61</v>
       </c>
     </row>
     <row r="234">
@@ -4179,7 +4179,7 @@
         <v>8</v>
       </c>
       <c r="D234" t="n">
-        <v>14959.57</v>
+        <v>17020.45</v>
       </c>
     </row>
     <row r="235">
@@ -4195,7 +4195,7 @@
         <v>8</v>
       </c>
       <c r="D235" t="n">
-        <v>17152.21</v>
+        <v>19843.55</v>
       </c>
     </row>
     <row r="236">
@@ -4211,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="D236" t="n">
-        <v>29365.43</v>
+        <v>27144.92</v>
       </c>
     </row>
     <row r="237">
@@ -4227,7 +4227,7 @@
         <v>8</v>
       </c>
       <c r="D237" t="n">
-        <v>10355.97</v>
+        <v>17487.07</v>
       </c>
     </row>
     <row r="238">
@@ -4243,7 +4243,7 @@
         <v>8</v>
       </c>
       <c r="D238" t="n">
-        <v>7756.34</v>
+        <v>10730.67</v>
       </c>
     </row>
     <row r="239">
@@ -4259,7 +4259,7 @@
         <v>8</v>
       </c>
       <c r="D239" t="n">
-        <v>4241.64</v>
+        <v>3865.82</v>
       </c>
     </row>
     <row r="240">
@@ -4275,7 +4275,7 @@
         <v>8</v>
       </c>
       <c r="D240" t="n">
-        <v>8270.73</v>
+        <v>10833.51</v>
       </c>
     </row>
     <row r="241">
@@ -4291,7 +4291,7 @@
         <v>8</v>
       </c>
       <c r="D241" t="n">
-        <v>15136.99</v>
+        <v>14020.34</v>
       </c>
     </row>
     <row r="242">
@@ -4307,7 +4307,7 @@
         <v>8</v>
       </c>
       <c r="D242" t="n">
-        <v>17946.88</v>
+        <v>19837.75</v>
       </c>
     </row>
     <row r="243">
@@ -4323,7 +4323,7 @@
         <v>8</v>
       </c>
       <c r="D243" t="n">
-        <v>30046.83</v>
+        <v>30268.4</v>
       </c>
     </row>
     <row r="244">
@@ -4339,7 +4339,7 @@
         <v>8</v>
       </c>
       <c r="D244" t="n">
-        <v>14431.47</v>
+        <v>16849.55</v>
       </c>
     </row>
     <row r="245">
@@ -4355,7 +4355,7 @@
         <v>9</v>
       </c>
       <c r="D245" t="n">
-        <v>7707.23</v>
+        <v>10859.85</v>
       </c>
     </row>
     <row r="246">
@@ -4371,7 +4371,7 @@
         <v>9</v>
       </c>
       <c r="D246" t="n">
-        <v>4305.79</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="247">
@@ -4387,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="D247" t="n">
-        <v>9065.4</v>
+        <v>10195.99</v>
       </c>
     </row>
     <row r="248">
@@ -4403,7 +4403,7 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>15087.88</v>
+        <v>17278.8</v>
       </c>
     </row>
     <row r="249">
@@ -4419,7 +4419,7 @@
         <v>9</v>
       </c>
       <c r="D249" t="n">
-        <v>18011.03</v>
+        <v>19966.93</v>
       </c>
     </row>
     <row r="250">
@@ -4435,7 +4435,7 @@
         <v>9</v>
       </c>
       <c r="D250" t="n">
-        <v>30110.99</v>
+        <v>30397.58</v>
       </c>
     </row>
     <row r="251">
@@ -4451,7 +4451,7 @@
         <v>9</v>
       </c>
       <c r="D251" t="n">
-        <v>14495.63</v>
+        <v>16978.73</v>
       </c>
     </row>
     <row r="252">
@@ -4467,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="D252" t="n">
-        <v>7771.39</v>
+        <v>10989.02</v>
       </c>
     </row>
     <row r="253">
@@ -4483,7 +4483,7 @@
         <v>9</v>
       </c>
       <c r="D253" t="n">
-        <v>4256.68</v>
+        <v>7253.46</v>
       </c>
     </row>
     <row r="254">
@@ -4499,7 +4499,7 @@
         <v>9</v>
       </c>
       <c r="D254" t="n">
-        <v>9129.549999999999</v>
+        <v>10325.17</v>
       </c>
     </row>
     <row r="255">
@@ -4515,7 +4515,7 @@
         <v>9</v>
       </c>
       <c r="D255" t="n">
-        <v>15152.04</v>
+        <v>17407.98</v>
       </c>
     </row>
     <row r="256">
@@ -4531,7 +4531,7 @@
         <v>9</v>
       </c>
       <c r="D256" t="n">
-        <v>17457.95</v>
+        <v>17101.8</v>
       </c>
     </row>
     <row r="257">
@@ -4547,7 +4547,7 @@
         <v>9</v>
       </c>
       <c r="D257" t="n">
-        <v>26163.79</v>
+        <v>30661.74</v>
       </c>
     </row>
     <row r="258">
@@ -4563,7 +4563,7 @@
         <v>9</v>
       </c>
       <c r="D258" t="n">
-        <v>14559.78</v>
+        <v>17107.9</v>
       </c>
     </row>
     <row r="259">
@@ -4579,7 +4579,7 @@
         <v>9</v>
       </c>
       <c r="D259" t="n">
-        <v>4554.71</v>
+        <v>11749.92</v>
       </c>
     </row>
     <row r="260">
@@ -4595,7 +4595,7 @@
         <v>9</v>
       </c>
       <c r="D260" t="n">
-        <v>1040</v>
+        <v>7382.63</v>
       </c>
     </row>
     <row r="261">
@@ -4611,7 +4611,7 @@
         <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>8576.469999999999</v>
+        <v>7460.04</v>
       </c>
     </row>
     <row r="262">
@@ -4627,7 +4627,7 @@
         <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>13052.52</v>
+        <v>18168.88</v>
       </c>
     </row>
     <row r="263">
@@ -4643,7 +4643,7 @@
         <v>9</v>
       </c>
       <c r="D263" t="n">
-        <v>18139.34</v>
+        <v>20225.28</v>
       </c>
     </row>
     <row r="264">
@@ -4659,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="D264" t="n">
-        <v>29622.05</v>
+        <v>27661.63</v>
       </c>
     </row>
     <row r="265">
@@ -4675,7 +4675,7 @@
         <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>13893.43</v>
+        <v>17372.06</v>
       </c>
     </row>
     <row r="266">
@@ -4691,7 +4691,7 @@
         <v>9</v>
       </c>
       <c r="D266" t="n">
-        <v>8630.209999999999</v>
+        <v>11112.4</v>
       </c>
     </row>
     <row r="267">
@@ -4707,7 +4707,7 @@
         <v>9</v>
       </c>
       <c r="D267" t="n">
-        <v>1104.16</v>
+        <v>8143.53</v>
       </c>
     </row>
     <row r="268">
@@ -4723,7 +4723,7 @@
         <v>9</v>
       </c>
       <c r="D268" t="n">
-        <v>5246.52</v>
+        <v>11350.22</v>
       </c>
     </row>
     <row r="269">
@@ -4739,7 +4739,7 @@
         <v>9</v>
       </c>
       <c r="D269" t="n">
-        <v>13116.68</v>
+        <v>18298.06</v>
       </c>
     </row>
     <row r="270">
@@ -4755,7 +4755,7 @@
         <v>9</v>
       </c>
       <c r="D270" t="n">
-        <v>17472.99</v>
+        <v>20489.44</v>
       </c>
     </row>
     <row r="271">
@@ -4771,7 +4771,7 @@
         <v>9</v>
       </c>
       <c r="D271" t="n">
-        <v>29572.94</v>
+        <v>30920.09</v>
       </c>
     </row>
     <row r="272">
@@ -4787,7 +4787,7 @@
         <v>9</v>
       </c>
       <c r="D272" t="n">
-        <v>10676.75</v>
+        <v>17366.26</v>
       </c>
     </row>
     <row r="273">
@@ -4803,7 +4803,7 @@
         <v>9</v>
       </c>
       <c r="D273" t="n">
-        <v>4683.02</v>
+        <v>11241.58</v>
       </c>
     </row>
     <row r="274">
@@ -4819,7 +4819,7 @@
         <v>9</v>
       </c>
       <c r="D274" t="n">
-        <v>5179.66</v>
+        <v>7506.01</v>
       </c>
     </row>
     <row r="275">
@@ -4835,7 +4835,7 @@
         <v>10</v>
       </c>
       <c r="D275" t="n">
-        <v>9322.02</v>
+        <v>10712.7</v>
       </c>
     </row>
     <row r="276">
@@ -4851,7 +4851,7 @@
         <v>10</v>
       </c>
       <c r="D276" t="n">
-        <v>15344.5</v>
+        <v>17795.51</v>
       </c>
     </row>
     <row r="277">
@@ -4867,7 +4867,7 @@
         <v>10</v>
       </c>
       <c r="D277" t="n">
-        <v>17537.14</v>
+        <v>20618.62</v>
       </c>
     </row>
     <row r="278">
@@ -4883,7 +4883,7 @@
         <v>10</v>
       </c>
       <c r="D278" t="n">
-        <v>26356.26</v>
+        <v>30914.29</v>
       </c>
     </row>
     <row r="279">
@@ -4899,7 +4899,7 @@
         <v>10</v>
       </c>
       <c r="D279" t="n">
-        <v>10740.9</v>
+        <v>18262.14</v>
       </c>
     </row>
     <row r="280">
@@ -4915,7 +4915,7 @@
         <v>10</v>
       </c>
       <c r="D280" t="n">
-        <v>4747.17</v>
+        <v>12137.46</v>
       </c>
     </row>
     <row r="281">
@@ -4931,7 +4931,7 @@
         <v>10</v>
       </c>
       <c r="D281" t="n">
-        <v>1232.47</v>
+        <v>7635.19</v>
       </c>
     </row>
     <row r="282">
@@ -4947,7 +4947,7 @@
         <v>10</v>
       </c>
       <c r="D282" t="n">
-        <v>9386.17</v>
+        <v>10841.88</v>
       </c>
     </row>
     <row r="283">
@@ -4963,7 +4963,7 @@
         <v>10</v>
       </c>
       <c r="D283" t="n">
-        <v>15408.66</v>
+        <v>17924.69</v>
       </c>
     </row>
     <row r="284">
@@ -4979,7 +4979,7 @@
         <v>10</v>
       </c>
       <c r="D284" t="n">
-        <v>17601.3</v>
+        <v>20747.79</v>
       </c>
     </row>
     <row r="285">
@@ -4995,7 +4995,7 @@
         <v>10</v>
       </c>
       <c r="D285" t="n">
-        <v>29814.52</v>
+        <v>28049.16</v>
       </c>
     </row>
     <row r="286">
@@ -5011,7 +5011,7 @@
         <v>10</v>
       </c>
       <c r="D286" t="n">
-        <v>10805.06</v>
+        <v>17759.59</v>
       </c>
     </row>
     <row r="287">
@@ -5027,7 +5027,7 @@
         <v>10</v>
       </c>
       <c r="D287" t="n">
-        <v>8205.43</v>
+        <v>8505.629999999999</v>
       </c>
     </row>
     <row r="288">
@@ -5043,7 +5043,7 @@
         <v>10</v>
       </c>
       <c r="D288" t="n">
-        <v>4577.46</v>
+        <v>7899.34</v>
       </c>
     </row>
     <row r="289">
@@ -5059,7 +5059,7 @@
         <v>10</v>
       </c>
       <c r="D289" t="n">
-        <v>8719.82</v>
+        <v>11106.03</v>
       </c>
     </row>
     <row r="290">
@@ -5075,7 +5075,7 @@
         <v>10</v>
       </c>
       <c r="D290" t="n">
-        <v>15472.81</v>
+        <v>18053.87</v>
       </c>
     </row>
     <row r="291">
@@ -5091,7 +5091,7 @@
         <v>10</v>
       </c>
       <c r="D291" t="n">
-        <v>15501.78</v>
+        <v>20876.97</v>
       </c>
     </row>
     <row r="292">
@@ -5107,7 +5107,7 @@
         <v>10</v>
       </c>
       <c r="D292" t="n">
-        <v>29878.67</v>
+        <v>28178.34</v>
       </c>
     </row>
     <row r="293">
@@ -5123,7 +5123,7 @@
         <v>10</v>
       </c>
       <c r="D293" t="n">
-        <v>14263.32</v>
+        <v>14759.48</v>
       </c>
     </row>
     <row r="294">
@@ -5139,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="D294" t="n">
-        <v>4875.48</v>
+        <v>11629.11</v>
       </c>
     </row>
     <row r="295">
@@ -5155,7 +5155,7 @@
         <v>10</v>
       </c>
       <c r="D295" t="n">
-        <v>4641.61</v>
+        <v>8028.52</v>
       </c>
     </row>
     <row r="296">
@@ -5171,7 +5171,7 @@
         <v>10</v>
       </c>
       <c r="D296" t="n">
-        <v>8897.24</v>
+        <v>8105.92</v>
       </c>
     </row>
     <row r="297">
@@ -5187,7 +5187,7 @@
         <v>10</v>
       </c>
       <c r="D297" t="n">
-        <v>15536.97</v>
+        <v>18183.04</v>
       </c>
     </row>
     <row r="298">
@@ -5203,7 +5203,7 @@
         <v>10</v>
       </c>
       <c r="D298" t="n">
-        <v>15565.94</v>
+        <v>20871.17</v>
       </c>
     </row>
     <row r="299">
@@ -5219,7 +5219,7 @@
         <v>10</v>
       </c>
       <c r="D299" t="n">
-        <v>29942.83</v>
+        <v>28307.52</v>
       </c>
     </row>
     <row r="300">
@@ -5235,7 +5235,7 @@
         <v>10</v>
       </c>
       <c r="D300" t="n">
-        <v>10933.37</v>
+        <v>18649.67</v>
       </c>
     </row>
     <row r="301">
@@ -5251,7 +5251,7 @@
         <v>10</v>
       </c>
       <c r="D301" t="n">
-        <v>8333.74</v>
+        <v>8763.98</v>
       </c>
     </row>
     <row r="302">
@@ -5267,7 +5267,7 @@
         <v>10</v>
       </c>
       <c r="D302" t="n">
-        <v>4819.04</v>
+        <v>5028.41</v>
       </c>
     </row>
     <row r="303">
@@ -5283,7 +5283,7 @@
         <v>10</v>
       </c>
       <c r="D303" t="n">
-        <v>8848.129999999999</v>
+        <v>11364.39</v>
       </c>
     </row>
     <row r="304">
@@ -5299,7 +5299,7 @@
         <v>10</v>
       </c>
       <c r="D304" t="n">
-        <v>15601.12</v>
+        <v>18312.22</v>
       </c>
     </row>
     <row r="305">
@@ -5315,7 +5315,7 @@
         <v>10</v>
       </c>
       <c r="D305" t="n">
-        <v>16517.65</v>
+        <v>23792.5</v>
       </c>
     </row>
     <row r="306">
@@ -5331,7 +5331,7 @@
         <v>11</v>
       </c>
       <c r="D306" t="n">
-        <v>26612.88</v>
+        <v>32197.7</v>
       </c>
     </row>
     <row r="307">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="D307" t="n">
-        <v>15008.87</v>
+        <v>18012.14</v>
       </c>
     </row>
     <row r="308">
@@ -5363,7 +5363,7 @@
         <v>11</v>
       </c>
       <c r="D308" t="n">
-        <v>8284.629999999999</v>
+        <v>12022.44</v>
       </c>
     </row>
     <row r="309">
@@ -5379,7 +5379,7 @@
         <v>11</v>
       </c>
       <c r="D309" t="n">
-        <v>4769.92</v>
+        <v>8286.870000000001</v>
       </c>
     </row>
     <row r="310">
@@ -5395,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="D310" t="n">
-        <v>5631.45</v>
+        <v>11358.58</v>
       </c>
     </row>
     <row r="311">
@@ -5411,7 +5411,7 @@
         <v>11</v>
       </c>
       <c r="D311" t="n">
-        <v>15665.28</v>
+        <v>18441.4</v>
       </c>
     </row>
     <row r="312">
@@ -5427,7 +5427,7 @@
         <v>11</v>
       </c>
       <c r="D312" t="n">
-        <v>17857.92</v>
+        <v>21264.5</v>
       </c>
     </row>
     <row r="313">
@@ -5443,7 +5443,7 @@
         <v>11</v>
       </c>
       <c r="D313" t="n">
-        <v>30071.14</v>
+        <v>28565.87</v>
       </c>
     </row>
     <row r="314">
@@ -5459,7 +5459,7 @@
         <v>11</v>
       </c>
       <c r="D314" t="n">
-        <v>14455.78</v>
+        <v>15147.02</v>
       </c>
     </row>
     <row r="315">
@@ -5475,7 +5475,7 @@
         <v>11</v>
       </c>
       <c r="D315" t="n">
-        <v>9079.290000000001</v>
+        <v>12016.64</v>
       </c>
     </row>
     <row r="316">
@@ -5491,7 +5491,7 @@
         <v>11</v>
       </c>
       <c r="D316" t="n">
-        <v>1553.24</v>
+        <v>8281.07</v>
       </c>
     </row>
     <row r="317">
@@ -5507,7 +5507,7 @@
         <v>11</v>
       </c>
       <c r="D317" t="n">
-        <v>5695.6</v>
+        <v>12254.46</v>
       </c>
     </row>
     <row r="318">
@@ -5523,7 +5523,7 @@
         <v>11</v>
       </c>
       <c r="D318" t="n">
-        <v>15729.43</v>
+        <v>18570.58</v>
       </c>
     </row>
     <row r="319">
@@ -5539,7 +5539,7 @@
         <v>11</v>
       </c>
       <c r="D319" t="n">
-        <v>18035.34</v>
+        <v>18264.4</v>
       </c>
     </row>
     <row r="320">
@@ -5555,7 +5555,7 @@
         <v>11</v>
       </c>
       <c r="D320" t="n">
-        <v>30135.29</v>
+        <v>28695.05</v>
       </c>
     </row>
     <row r="321">
@@ -5571,7 +5571,7 @@
         <v>11</v>
       </c>
       <c r="D321" t="n">
-        <v>14406.67</v>
+        <v>18405.48</v>
       </c>
     </row>
     <row r="322">
@@ -5587,7 +5587,7 @@
         <v>11</v>
       </c>
       <c r="D322" t="n">
-        <v>8412.940000000001</v>
+        <v>12280.8</v>
       </c>
     </row>
     <row r="323">
@@ -5603,7 +5603,7 @@
         <v>11</v>
       </c>
       <c r="D323" t="n">
-        <v>1617.4</v>
+        <v>9176.950000000001</v>
       </c>
     </row>
     <row r="324">
@@ -5619,7 +5619,7 @@
         <v>11</v>
       </c>
       <c r="D324" t="n">
-        <v>5759.76</v>
+        <v>12383.64</v>
       </c>
     </row>
     <row r="325">
@@ -5635,7 +5635,7 @@
         <v>11</v>
       </c>
       <c r="D325" t="n">
-        <v>15793.59</v>
+        <v>18699.75</v>
       </c>
     </row>
     <row r="326">
@@ -5651,7 +5651,7 @@
         <v>11</v>
       </c>
       <c r="D326" t="n">
-        <v>18716.74</v>
+        <v>21387.88</v>
       </c>
     </row>
     <row r="327">
@@ -5667,7 +5667,7 @@
         <v>11</v>
       </c>
       <c r="D327" t="n">
-        <v>26805.35</v>
+        <v>32585.23</v>
       </c>
     </row>
     <row r="328">
@@ -5683,7 +5683,7 @@
         <v>11</v>
       </c>
       <c r="D328" t="n">
-        <v>11189.99</v>
+        <v>18534.65</v>
       </c>
     </row>
     <row r="329">
@@ -5699,7 +5699,7 @@
         <v>11</v>
       </c>
       <c r="D329" t="n">
-        <v>5196.26</v>
+        <v>13041.7</v>
       </c>
     </row>
     <row r="330">
@@ -5715,7 +5715,7 @@
         <v>11</v>
       </c>
       <c r="D330" t="n">
-        <v>4962.39</v>
+        <v>8674.41</v>
       </c>
     </row>
     <row r="331">
@@ -5731,7 +5731,7 @@
         <v>11</v>
       </c>
       <c r="D331" t="n">
-        <v>9218.02</v>
+        <v>8751.809999999999</v>
       </c>
     </row>
     <row r="332">
@@ -5747,7 +5747,7 @@
         <v>11</v>
       </c>
       <c r="D332" t="n">
-        <v>15857.74</v>
+        <v>18828.93</v>
       </c>
     </row>
     <row r="333">
@@ -5763,7 +5763,7 @@
         <v>11</v>
       </c>
       <c r="D333" t="n">
-        <v>15886.71</v>
+        <v>21517.06</v>
       </c>
     </row>
     <row r="334">
@@ -5779,7 +5779,7 @@
         <v>11</v>
       </c>
       <c r="D334" t="n">
-        <v>30263.6</v>
+        <v>28953.4</v>
       </c>
     </row>
     <row r="335">
@@ -5795,7 +5795,7 @@
         <v>11</v>
       </c>
       <c r="D335" t="n">
-        <v>14648.25</v>
+        <v>15534.55</v>
       </c>
     </row>
     <row r="336">
@@ -5811,7 +5811,7 @@
         <v>12</v>
       </c>
       <c r="D336" t="n">
-        <v>8654.52</v>
+        <v>9409.870000000001</v>
       </c>
     </row>
     <row r="337">
@@ -5827,7 +5827,7 @@
         <v>12</v>
       </c>
       <c r="D337" t="n">
-        <v>5139.81</v>
+        <v>5674.3</v>
       </c>
     </row>
     <row r="338">
@@ -5843,7 +5843,7 @@
         <v>12</v>
       </c>
       <c r="D338" t="n">
-        <v>9899.41</v>
+        <v>11875.29</v>
       </c>
     </row>
     <row r="339">
@@ -5859,7 +5859,7 @@
         <v>12</v>
       </c>
       <c r="D339" t="n">
-        <v>13758.23</v>
+        <v>19589.83</v>
       </c>
     </row>
     <row r="340">
@@ -5875,7 +5875,7 @@
         <v>12</v>
       </c>
       <c r="D340" t="n">
-        <v>18114.54</v>
+        <v>21781.21</v>
       </c>
     </row>
     <row r="341">
@@ -5891,7 +5891,7 @@
         <v>12</v>
       </c>
       <c r="D341" t="n">
-        <v>30327.76</v>
+        <v>29082.58</v>
       </c>
     </row>
     <row r="342">
@@ -5907,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="D342" t="n">
-        <v>14599.13</v>
+        <v>18793.01</v>
       </c>
     </row>
     <row r="343">
@@ -5923,7 +5923,7 @@
         <v>12</v>
       </c>
       <c r="D343" t="n">
-        <v>8605.4</v>
+        <v>12668.33</v>
       </c>
     </row>
     <row r="344">
@@ -5939,7 +5939,7 @@
         <v>12</v>
       </c>
       <c r="D344" t="n">
-        <v>5090.7</v>
+        <v>5803.48</v>
       </c>
     </row>
     <row r="345">
@@ -5955,7 +5955,7 @@
         <v>12</v>
       </c>
       <c r="D345" t="n">
-        <v>9233.059999999999</v>
+        <v>12139.45</v>
       </c>
     </row>
     <row r="346">
@@ -5971,7 +5971,7 @@
         <v>12</v>
       </c>
       <c r="D346" t="n">
-        <v>15986.05</v>
+        <v>19087.28</v>
       </c>
     </row>
     <row r="347">
@@ -5987,7 +5987,7 @@
         <v>12</v>
       </c>
       <c r="D347" t="n">
-        <v>16015.02</v>
+        <v>22542.11</v>
       </c>
     </row>
     <row r="348">
@@ -6003,7 +6003,7 @@
         <v>12</v>
       </c>
       <c r="D348" t="n">
-        <v>26997.81</v>
+        <v>32972.76</v>
       </c>
     </row>
     <row r="349">
@@ -6019,7 +6019,7 @@
         <v>12</v>
       </c>
       <c r="D349" t="n">
-        <v>14776.56</v>
+        <v>15792.9</v>
       </c>
     </row>
     <row r="350">
@@ -6035,7 +6035,7 @@
         <v>12</v>
       </c>
       <c r="D350" t="n">
-        <v>8669.559999999999</v>
+        <v>12797.5</v>
       </c>
     </row>
     <row r="351">
@@ -6051,7 +6051,7 @@
         <v>12</v>
       </c>
       <c r="D351" t="n">
-        <v>1874.02</v>
+        <v>9693.66</v>
       </c>
     </row>
     <row r="352">
@@ -6067,7 +6067,7 @@
         <v>12</v>
       </c>
       <c r="D352" t="n">
-        <v>9297.209999999999</v>
+        <v>12268.63</v>
       </c>
     </row>
     <row r="353">
@@ -6083,7 +6083,7 @@
         <v>12</v>
       </c>
       <c r="D353" t="n">
-        <v>16780.72</v>
+        <v>19081.48</v>
       </c>
     </row>
     <row r="354">
@@ -6099,7 +6099,7 @@
         <v>12</v>
       </c>
       <c r="D354" t="n">
-        <v>16079.18</v>
+        <v>22671.29</v>
       </c>
     </row>
     <row r="355">
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="D355" t="n">
-        <v>30342.8</v>
+        <v>29340.93</v>
       </c>
     </row>
     <row r="356">
@@ -6131,7 +6131,7 @@
         <v>12</v>
       </c>
       <c r="D356" t="n">
-        <v>14840.71</v>
+        <v>15922.08</v>
       </c>
     </row>
     <row r="357">
@@ -6147,7 +6147,7 @@
         <v>12</v>
       </c>
       <c r="D357" t="n">
-        <v>5452.88</v>
+        <v>13558.4</v>
       </c>
     </row>
     <row r="358">
@@ -6163,7 +6163,7 @@
         <v>12</v>
       </c>
       <c r="D358" t="n">
-        <v>5332.28</v>
+        <v>6061.83</v>
       </c>
     </row>
     <row r="359">
@@ -6179,7 +6179,7 @@
         <v>12</v>
       </c>
       <c r="D359" t="n">
-        <v>6968.09</v>
+        <v>14423.26</v>
       </c>
     </row>
     <row r="360">
@@ -6195,7 +6195,7 @@
         <v>12</v>
       </c>
       <c r="D360" t="n">
-        <v>17732.43</v>
+        <v>21236.11</v>
       </c>
     </row>
     <row r="361">
@@ -6211,7 +6211,7 @@
         <v>12</v>
       </c>
       <c r="D361" t="n">
-        <v>17030.89</v>
+        <v>24194.2</v>
       </c>
     </row>
     <row r="362">
@@ -6227,7 +6227,7 @@
         <v>12</v>
       </c>
       <c r="D362" t="n">
-        <v>30406.96</v>
+        <v>32599.39</v>
       </c>
     </row>
     <row r="363">
@@ -6243,7 +6243,7 @@
         <v>12</v>
       </c>
       <c r="D363" t="n">
-        <v>11510.76</v>
+        <v>19812.26</v>
       </c>
     </row>
     <row r="364">
@@ -6259,7 +6259,7 @@
         <v>12</v>
       </c>
       <c r="D364" t="n">
-        <v>8797.870000000001</v>
+        <v>13055.86</v>
       </c>
     </row>
     <row r="365">
@@ -6275,7 +6275,7 @@
         <v>12</v>
       </c>
       <c r="D365" t="n">
-        <v>5283.16</v>
+        <v>9320.290000000001</v>
       </c>
     </row>
     <row r="366">
@@ -6291,7 +6291,7 @@
         <v>12</v>
       </c>
       <c r="D366" t="n">
-        <v>10156.03</v>
+        <v>12392</v>
       </c>
     </row>
   </sheetData>
